--- a/事業計画/ティエリーマルクス・ブラッスリー_5か年事業計画_FY2027-2031_rev2.xlsx
+++ b/事業計画/ティエリーマルクス・ブラッスリー_5か年事業計画_FY2027-2031_rev2.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="159">
   <si>
     <r>
       <rPr>
@@ -1933,27 +1933,6 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">号店
 </t>
     </r>
@@ -1976,7 +1955,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">東京・札幌・大阪</t>
+      <t xml:space="preserve">六本木</t>
     </r>
     <r>
       <rPr>
@@ -2000,6 +1979,83 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号店
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">札幌・大阪</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">4</t>
     </r>
     <r>
@@ -2183,46 +2239,72 @@
     <t xml:space="preserve">非償却・退去時返還対象</t>
   </si>
   <si>
-    <t xml:space="preserve">ワイン＋美術品</t>
-  </si>
-  <si>
-    <t xml:space="preserve">非償却（棚卸資産・美術品）</t>
+    <t xml:space="preserve">ワイン・美術品在庫</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号店は美術品を含む。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号店以降はワイン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円のみ（非償却）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">初期投資　合計</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">償却対象資産（＝合計－保証金－ワイン</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美術品）</t>
-    </r>
+    <t xml:space="preserve">償却対象資産（＝合計－保証金－ワイン・美術品在庫）</t>
   </si>
   <si>
     <r>
@@ -3272,7 +3354,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">分割払いスキーム反映。</t>
+      <t xml:space="preserve">分割払いスキーム反映。初期投資は</t>
     </r>
     <r>
       <rPr>
@@ -3291,7 +3373,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">店あたり初期投資</t>
+      <t xml:space="preserve">号店</t>
     </r>
     <r>
       <rPr>
@@ -3310,7 +3392,102 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">百万円のうち</t>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号店</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">257.25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号店以降</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">252.25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円。うち</t>
     </r>
     <r>
       <rPr>
@@ -3329,26 +3506,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">百万円を分割（開業時現金支出</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">158.35</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円）。</t>
+      <t xml:space="preserve">百万円を分割。</t>
     </r>
   </si>
   <si>
@@ -3618,63 +3776,91 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FFC00000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">※ 1</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ ワイン・美術品在庫は</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">店あたり初期投資が</t>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FFC00000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">247→297.25</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号店</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円に増加（ワイン＋美術品</t>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FFC00000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">50</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円（美術品含む）、</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円）。</t>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号店以降はワインのみ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
         <rFont val="Meiryo"/>
         <family val="0"/>
         <charset val="1"/>
@@ -3688,7 +3874,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">店舗で</t>
+      <t xml:space="preserve">店舗累計の初期投資は</t>
     </r>
     <r>
       <rPr>
@@ -3698,7 +3884,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">22.3</t>
+      <t xml:space="preserve">23.3</t>
     </r>
     <r>
       <rPr>
@@ -3707,26 +3893,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">億→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">26.8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億。</t>
+      <t xml:space="preserve">億円。</t>
     </r>
   </si>
 </sst>
@@ -4000,7 +4167,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4199,10 +4366,6 @@
     </xf>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -4904,7 +5067,7 @@
       </c>
       <c r="B29" s="18" t="n">
         <f aca="false">投資・キャッシュフロー!H6</f>
-        <v>-2645.25</v>
+        <v>-2325.25</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4913,7 +5076,7 @@
       </c>
       <c r="B30" s="18" t="n">
         <f aca="false">投資・キャッシュフロー!H8</f>
-        <v>-1395.15</v>
+        <v>-1075.15</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4922,7 +5085,7 @@
       </c>
       <c r="B31" s="18" t="n">
         <f aca="false">投資・キャッシュフロー!B18</f>
-        <v>851.89471456</v>
+        <v>534.46849765</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4940,7 +5103,7 @@
       </c>
       <c r="B33" s="19" t="n">
         <f aca="false">投資・キャッシュフロー!B22</f>
-        <v>-501.89471456</v>
+        <v>-184.46849765</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5320,24 +5483,30 @@
       <c r="C31" s="26" t="s">
         <v>86</v>
       </c>
+      <c r="D31" s="26" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B32" s="22" t="n">
         <v>10</v>
       </c>
       <c r="C32" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" s="22" t="n">
         <v>5</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B33" s="22" t="n">
         <v>194.25</v>
@@ -5345,13 +5514,16 @@
       <c r="C33" s="22" t="n">
         <v>194.25</v>
       </c>
+      <c r="D33" s="22" t="n">
+        <v>194.25</v>
+      </c>
       <c r="H33" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B34" s="22" t="n">
         <v>4</v>
@@ -5359,11 +5531,14 @@
       <c r="C34" s="22" t="n">
         <v>4</v>
       </c>
+      <c r="D34" s="22" t="n">
+        <v>4</v>
+      </c>
       <c r="H34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B35" s="22" t="n">
         <v>39</v>
@@ -5371,27 +5546,33 @@
       <c r="C35" s="22" t="n">
         <v>39</v>
       </c>
+      <c r="D35" s="22" t="n">
+        <v>39</v>
+      </c>
       <c r="H35" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B36" s="22" t="n">
         <v>50</v>
       </c>
       <c r="C36" s="22" t="n">
-        <v>50</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>95</v>
+        <v>10</v>
+      </c>
+      <c r="D36" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H36" s="24" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B37" s="28" t="n">
         <f aca="false">SUM(B32:B36)</f>
@@ -5399,12 +5580,16 @@
       </c>
       <c r="C37" s="28" t="n">
         <f aca="false">SUM(C32:C36)</f>
-        <v>292.25</v>
+        <v>257.25</v>
+      </c>
+      <c r="D37" s="28" t="n">
+        <f aca="false">SUM(D32:D36)</f>
+        <v>252.25</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B38" s="29" t="n">
         <f aca="false">B37-B35-B36</f>
@@ -5412,15 +5597,19 @@
       </c>
       <c r="C38" s="29" t="n">
         <f aca="false">C37-C35-C36</f>
+        <v>208.25</v>
+      </c>
+      <c r="D38" s="29" t="n">
+        <f aca="false">D37-D35-D36</f>
         <v>203.25</v>
       </c>
       <c r="H38" s="30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B39" s="22" t="n">
         <v>10</v>
@@ -5428,10 +5617,13 @@
       <c r="C39" s="22" t="n">
         <v>10</v>
       </c>
+      <c r="D39" s="22" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B40" s="29" t="n">
         <f aca="false">B38/B39</f>
@@ -5439,12 +5631,16 @@
       </c>
       <c r="C40" s="29" t="n">
         <f aca="false">C38/C39</f>
+        <v>20.825</v>
+      </c>
+      <c r="D40" s="29" t="n">
+        <f aca="false">D38/D39</f>
         <v>20.325</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -5454,7 +5650,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B43" s="22" t="n">
         <v>138.9</v>
@@ -5462,7 +5658,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="31" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B44" s="29" t="n">
         <f aca="false">B37-$B$43</f>
@@ -5470,12 +5666,16 @@
       </c>
       <c r="C44" s="29" t="n">
         <f aca="false">C37-$B$43</f>
-        <v>153.35</v>
+        <v>118.35</v>
+      </c>
+      <c r="D44" s="29" t="n">
+        <f aca="false">D37-$B$43</f>
+        <v>113.35</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B45" s="22" t="n">
         <v>15.6</v>
@@ -5483,7 +5683,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -5513,7 +5713,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B49" s="32" t="n">
         <v>1</v>
@@ -5531,7 +5731,7 @@
         <v>2</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5561,7 +5761,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B51" s="22" t="n">
         <v>15</v>
@@ -5605,7 +5805,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5616,15 +5816,15 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>3</v>
@@ -5644,7 +5844,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -5655,7 +5855,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="35" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B6" s="32" t="n">
         <v>1</v>
@@ -5663,7 +5863,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" s="18" t="n">
         <f aca="false">前提条件!$B$10</f>
@@ -5672,7 +5872,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C8" s="32" t="n">
         <v>1</v>
@@ -5792,7 +5992,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="39" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C13" s="40" t="n">
         <f aca="false">C9-SUM(C10:C12)</f>
@@ -5892,7 +6092,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="41" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C17" s="40" t="n">
         <f aca="false">C13-SUM(C14:C16)</f>
@@ -5967,7 +6167,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="37" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C20" s="38" t="n">
         <f aca="false">IF(C8=0,0,前提条件!$B$13*$B$6*IF(C8=1,$B$7/12,1))</f>
@@ -5992,7 +6192,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C21" s="38" t="n">
         <f aca="false">IF(C8=0,0,MAX(0,C9/$B$6-前提条件!$B$15*IF(C8=1,$B$7/12,1))*前提条件!$B$14*$B$6)</f>
@@ -6017,7 +6217,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="37" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C22" s="38" t="n">
         <f aca="false">IF(C$8=0,0,C$9*INDEX(前提条件!$B$27:$D$27,1,C$8))</f>
@@ -6042,7 +6242,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C23" s="40" t="n">
         <f aca="false">C17-SUM(C18:C22)</f>
@@ -6092,7 +6292,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C25" s="40" t="n">
         <f aca="false">C23-C24</f>
@@ -6117,7 +6317,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -6128,7 +6328,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="35" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B28" s="32" t="n">
         <v>2</v>
@@ -6136,7 +6336,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B29" s="18" t="n">
         <f aca="false">前提条件!$B$9</f>
@@ -6145,7 +6345,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C30" s="32" t="n">
         <v>0</v>
@@ -6265,7 +6465,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="39" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C35" s="40" t="n">
         <f aca="false">C31-SUM(C32:C34)</f>
@@ -6365,7 +6565,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="41" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C39" s="40" t="n">
         <f aca="false">C35-SUM(C36:C38)</f>
@@ -6440,7 +6640,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="37" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C42" s="38" t="n">
         <f aca="false">IF(C30=0,0,前提条件!$B$13*$B$28*IF(C30=1,$B$29/12,1))</f>
@@ -6465,7 +6665,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="37" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C43" s="38" t="n">
         <f aca="false">IF(C30=0,0,MAX(0,C31/$B$28-前提条件!$B$15*IF(C30=1,$B$29/12,1))*前提条件!$B$14*$B$28)</f>
@@ -6490,7 +6690,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="37" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C44" s="38" t="n">
         <f aca="false">IF(C$30=0,0,C$31*INDEX(前提条件!$B$27:$D$27,1,C$30))</f>
@@ -6515,7 +6715,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C45" s="40" t="n">
         <f aca="false">C39-SUM(C40:C44)</f>
@@ -6543,29 +6743,29 @@
         <v>26</v>
       </c>
       <c r="C46" s="38" t="n">
-        <f aca="false">IF(C30=0,0,前提条件!$B$40*$B$28*IF(C30=1,$B$29/12,1))</f>
+        <f aca="false">IF(C30=0,0,前提条件!$C$40*$B$28*IF(C30=1,$B$29/12,1))</f>
         <v>0</v>
       </c>
       <c r="D46" s="38" t="n">
-        <f aca="false">IF(D30=0,0,前提条件!$B$40*$B$28*IF(D30=1,$B$29/12,1))</f>
+        <f aca="false">IF(D30=0,0,前提条件!$C$40*$B$28*IF(D30=1,$B$29/12,1))</f>
         <v>26.03125</v>
       </c>
       <c r="E46" s="38" t="n">
-        <f aca="false">IF(E30=0,0,前提条件!$B$40*$B$28*IF(E30=1,$B$29/12,1))</f>
+        <f aca="false">IF(E30=0,0,前提条件!$C$40*$B$28*IF(E30=1,$B$29/12,1))</f>
         <v>41.65</v>
       </c>
       <c r="F46" s="38" t="n">
-        <f aca="false">IF(F30=0,0,前提条件!$B$40*$B$28*IF(F30=1,$B$29/12,1))</f>
+        <f aca="false">IF(F30=0,0,前提条件!$C$40*$B$28*IF(F30=1,$B$29/12,1))</f>
         <v>41.65</v>
       </c>
       <c r="G46" s="38" t="n">
-        <f aca="false">IF(G30=0,0,前提条件!$B$40*$B$28*IF(G30=1,$B$29/12,1))</f>
+        <f aca="false">IF(G30=0,0,前提条件!$C$40*$B$28*IF(G30=1,$B$29/12,1))</f>
         <v>41.65</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C47" s="40" t="n">
         <f aca="false">C45-C46</f>
@@ -6590,7 +6790,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -6601,7 +6801,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="35" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B50" s="32" t="n">
         <v>2</v>
@@ -6609,7 +6809,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B51" s="18" t="n">
         <f aca="false">前提条件!$B$9</f>
@@ -6618,7 +6818,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C52" s="32" t="n">
         <v>0</v>
@@ -6738,7 +6938,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="39" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C57" s="40" t="n">
         <f aca="false">C53-SUM(C54:C56)</f>
@@ -6838,7 +7038,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="41" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C61" s="40" t="n">
         <f aca="false">C57-SUM(C58:C60)</f>
@@ -6913,7 +7113,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="37" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C64" s="38" t="n">
         <f aca="false">IF(C52=0,0,前提条件!$B$13*$B$50*IF(C52=1,$B$51/12,1))</f>
@@ -6938,7 +7138,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="37" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C65" s="38" t="n">
         <f aca="false">IF(C52=0,0,MAX(0,C53/$B$50-前提条件!$B$15*IF(C52=1,$B$51/12,1))*前提条件!$B$14*$B$50)</f>
@@ -6963,7 +7163,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="37" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C66" s="38" t="n">
         <f aca="false">IF(C$52=0,0,C$53*INDEX(前提条件!$B$27:$D$27,1,C$52))</f>
@@ -6988,7 +7188,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C67" s="40" t="n">
         <f aca="false">C61-SUM(C62:C66)</f>
@@ -7016,29 +7216,29 @@
         <v>26</v>
       </c>
       <c r="C68" s="38" t="n">
-        <f aca="false">IF(C52=0,0,前提条件!$C$40*$B$50*IF(C52=1,$B$51/12,1))</f>
+        <f aca="false">IF(C52=0,0,前提条件!$D$40*$B$50*IF(C52=1,$B$51/12,1))</f>
         <v>0</v>
       </c>
       <c r="D68" s="38" t="n">
-        <f aca="false">IF(D52=0,0,前提条件!$C$40*$B$50*IF(D52=1,$B$51/12,1))</f>
+        <f aca="false">IF(D52=0,0,前提条件!$D$40*$B$50*IF(D52=1,$B$51/12,1))</f>
         <v>0</v>
       </c>
       <c r="E68" s="38" t="n">
-        <f aca="false">IF(E52=0,0,前提条件!$C$40*$B$50*IF(E52=1,$B$51/12,1))</f>
+        <f aca="false">IF(E52=0,0,前提条件!$D$40*$B$50*IF(E52=1,$B$51/12,1))</f>
         <v>25.40625</v>
       </c>
       <c r="F68" s="38" t="n">
-        <f aca="false">IF(F52=0,0,前提条件!$C$40*$B$50*IF(F52=1,$B$51/12,1))</f>
+        <f aca="false">IF(F52=0,0,前提条件!$D$40*$B$50*IF(F52=1,$B$51/12,1))</f>
         <v>40.65</v>
       </c>
       <c r="G68" s="38" t="n">
-        <f aca="false">IF(G52=0,0,前提条件!$C$40*$B$50*IF(G52=1,$B$51/12,1))</f>
+        <f aca="false">IF(G52=0,0,前提条件!$D$40*$B$50*IF(G52=1,$B$51/12,1))</f>
         <v>40.65</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C69" s="40" t="n">
         <f aca="false">C67-C68</f>
@@ -7063,7 +7263,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -7074,7 +7274,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="35" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B72" s="32" t="n">
         <v>2</v>
@@ -7082,7 +7282,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B73" s="18" t="n">
         <f aca="false">前提条件!$B$9</f>
@@ -7091,7 +7291,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C74" s="32" t="n">
         <v>0</v>
@@ -7211,7 +7411,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="39" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C79" s="40" t="n">
         <f aca="false">C75-SUM(C76:C78)</f>
@@ -7311,7 +7511,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="41" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C83" s="40" t="n">
         <f aca="false">C79-SUM(C80:C82)</f>
@@ -7386,7 +7586,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="37" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C86" s="38" t="n">
         <f aca="false">IF(C74=0,0,前提条件!$B$13*$B$72*IF(C74=1,$B$73/12,1))</f>
@@ -7411,7 +7611,7 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="37" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C87" s="38" t="n">
         <f aca="false">IF(C74=0,0,MAX(0,C75/$B$72-前提条件!$B$15*IF(C74=1,$B$73/12,1))*前提条件!$B$14*$B$72)</f>
@@ -7436,7 +7636,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="37" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C88" s="38" t="n">
         <f aca="false">IF(C$74=0,0,C$75*INDEX(前提条件!$B$27:$D$27,1,C$74))</f>
@@ -7461,7 +7661,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C89" s="40" t="n">
         <f aca="false">C83-SUM(C84:C88)</f>
@@ -7489,29 +7689,29 @@
         <v>26</v>
       </c>
       <c r="C90" s="38" t="n">
-        <f aca="false">IF(C74=0,0,前提条件!$C$40*$B$72*IF(C74=1,$B$73/12,1))</f>
+        <f aca="false">IF(C74=0,0,前提条件!$D$40*$B$72*IF(C74=1,$B$73/12,1))</f>
         <v>0</v>
       </c>
       <c r="D90" s="38" t="n">
-        <f aca="false">IF(D74=0,0,前提条件!$C$40*$B$72*IF(D74=1,$B$73/12,1))</f>
+        <f aca="false">IF(D74=0,0,前提条件!$D$40*$B$72*IF(D74=1,$B$73/12,1))</f>
         <v>0</v>
       </c>
       <c r="E90" s="38" t="n">
-        <f aca="false">IF(E74=0,0,前提条件!$C$40*$B$72*IF(E74=1,$B$73/12,1))</f>
+        <f aca="false">IF(E74=0,0,前提条件!$D$40*$B$72*IF(E74=1,$B$73/12,1))</f>
         <v>0</v>
       </c>
       <c r="F90" s="38" t="n">
-        <f aca="false">IF(F74=0,0,前提条件!$C$40*$B$72*IF(F74=1,$B$73/12,1))</f>
+        <f aca="false">IF(F74=0,0,前提条件!$D$40*$B$72*IF(F74=1,$B$73/12,1))</f>
         <v>25.40625</v>
       </c>
       <c r="G90" s="38" t="n">
-        <f aca="false">IF(G74=0,0,前提条件!$C$40*$B$72*IF(G74=1,$B$73/12,1))</f>
+        <f aca="false">IF(G74=0,0,前提条件!$D$40*$B$72*IF(G74=1,$B$73/12,1))</f>
         <v>40.65</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C91" s="40" t="n">
         <f aca="false">C89-C90</f>
@@ -7536,7 +7736,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -7547,7 +7747,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="35" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B94" s="32" t="n">
         <v>2</v>
@@ -7555,7 +7755,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B95" s="18" t="n">
         <f aca="false">前提条件!$B$9</f>
@@ -7564,7 +7764,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C96" s="32" t="n">
         <v>0</v>
@@ -7684,7 +7884,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="39" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C101" s="40" t="n">
         <f aca="false">C97-SUM(C98:C100)</f>
@@ -7784,7 +7984,7 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="41" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C105" s="40" t="n">
         <f aca="false">C101-SUM(C102:C104)</f>
@@ -7859,7 +8059,7 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="37" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C108" s="38" t="n">
         <f aca="false">IF(C96=0,0,前提条件!$B$13*$B$94*IF(C96=1,$B$95/12,1))</f>
@@ -7884,7 +8084,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="37" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C109" s="38" t="n">
         <f aca="false">IF(C96=0,0,MAX(0,C97/$B$94-前提条件!$B$15*IF(C96=1,$B$95/12,1))*前提条件!$B$14*$B$94)</f>
@@ -7909,7 +8109,7 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="37" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C110" s="38" t="n">
         <f aca="false">IF(C$96=0,0,C$97*INDEX(前提条件!$B$27:$D$27,1,C$96))</f>
@@ -7934,7 +8134,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C111" s="40" t="n">
         <f aca="false">C105-SUM(C106:C110)</f>
@@ -7962,29 +8162,29 @@
         <v>26</v>
       </c>
       <c r="C112" s="38" t="n">
-        <f aca="false">IF(C96=0,0,前提条件!$C$40*$B$94*IF(C96=1,$B$95/12,1))</f>
+        <f aca="false">IF(C96=0,0,前提条件!$D$40*$B$94*IF(C96=1,$B$95/12,1))</f>
         <v>0</v>
       </c>
       <c r="D112" s="38" t="n">
-        <f aca="false">IF(D96=0,0,前提条件!$C$40*$B$94*IF(D96=1,$B$95/12,1))</f>
+        <f aca="false">IF(D96=0,0,前提条件!$D$40*$B$94*IF(D96=1,$B$95/12,1))</f>
         <v>0</v>
       </c>
       <c r="E112" s="38" t="n">
-        <f aca="false">IF(E96=0,0,前提条件!$C$40*$B$94*IF(E96=1,$B$95/12,1))</f>
+        <f aca="false">IF(E96=0,0,前提条件!$D$40*$B$94*IF(E96=1,$B$95/12,1))</f>
         <v>0</v>
       </c>
       <c r="F112" s="38" t="n">
-        <f aca="false">IF(F96=0,0,前提条件!$C$40*$B$94*IF(F96=1,$B$95/12,1))</f>
+        <f aca="false">IF(F96=0,0,前提条件!$D$40*$B$94*IF(F96=1,$B$95/12,1))</f>
         <v>0</v>
       </c>
       <c r="G112" s="38" t="n">
-        <f aca="false">IF(G96=0,0,前提条件!$C$40*$B$94*IF(G96=1,$B$95/12,1))</f>
+        <f aca="false">IF(G96=0,0,前提条件!$D$40*$B$94*IF(G96=1,$B$95/12,1))</f>
         <v>25.40625</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C113" s="40" t="n">
         <f aca="false">C111-C112</f>
@@ -8033,7 +8233,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8045,15 +8245,15 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>3</v>
@@ -8233,7 +8433,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="39" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B9" s="44" t="n">
         <f aca="false">IF($G$5=0,0,G9/$G$5)</f>
@@ -8365,7 +8565,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="41" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B13" s="44" t="n">
         <f aca="false">IF($G$5=0,0,G13/$G$5)</f>
@@ -8464,7 +8664,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B16" s="44" t="n">
         <f aca="false">IF($G$5=0,0,G16/$G$5)</f>
@@ -8497,7 +8697,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B17" s="44" t="n">
         <f aca="false">IF($G$5=0,0,G17/$G$5)</f>
@@ -8530,7 +8730,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="37" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B18" s="44" t="n">
         <f aca="false">IF($G$5=0,0,G18/$G$5)</f>
@@ -8563,7 +8763,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B19" s="44" t="n">
         <f aca="false">IF($G$5=0,0,G19/$G$5)</f>
@@ -8786,12 +8986,12 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -8821,7 +9021,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8833,7 +9033,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8915,36 +9115,36 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C6" s="38" t="n">
         <f aca="false">-C4*前提条件!$B$37</f>
         <v>-297.25</v>
       </c>
       <c r="D6" s="38" t="n">
-        <f aca="false">-D4*前提条件!$B$37</f>
-        <v>-594.5</v>
+        <f aca="false">-D4*前提条件!$C$37</f>
+        <v>-514.5</v>
       </c>
       <c r="E6" s="38" t="n">
-        <f aca="false">-E4*前提条件!$C$37</f>
-        <v>-584.5</v>
+        <f aca="false">-E4*前提条件!$D$37</f>
+        <v>-504.5</v>
       </c>
       <c r="F6" s="38" t="n">
-        <f aca="false">-F4*前提条件!$C$37</f>
-        <v>-584.5</v>
+        <f aca="false">-F4*前提条件!$D$37</f>
+        <v>-504.5</v>
       </c>
       <c r="G6" s="38" t="n">
-        <f aca="false">-G4*前提条件!$C$37</f>
-        <v>-584.5</v>
+        <f aca="false">-G4*前提条件!$D$37</f>
+        <v>-504.5</v>
       </c>
       <c r="H6" s="40" t="n">
         <f aca="false">SUM(C6:G6)</f>
-        <v>-2645.25</v>
+        <v>-2325.25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C7" s="38" t="n">
         <f aca="false">C4*前提条件!$B$43</f>
@@ -8973,7 +9173,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C8" s="40" t="n">
         <f aca="false">C6+C7</f>
@@ -8981,28 +9181,28 @@
       </c>
       <c r="D8" s="40" t="n">
         <f aca="false">D6+D7</f>
-        <v>-316.7</v>
+        <v>-236.7</v>
       </c>
       <c r="E8" s="40" t="n">
         <f aca="false">E6+E7</f>
-        <v>-306.7</v>
+        <v>-226.7</v>
       </c>
       <c r="F8" s="40" t="n">
         <f aca="false">F6+F7</f>
-        <v>-306.7</v>
+        <v>-226.7</v>
       </c>
       <c r="G8" s="40" t="n">
         <f aca="false">G6+G7</f>
-        <v>-306.7</v>
+        <v>-226.7</v>
       </c>
       <c r="H8" s="40" t="n">
         <f aca="false">SUM(C8:G8)</f>
-        <v>-1395.15</v>
+        <v>-1075.15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C9" s="38" t="n">
         <f aca="false">-(IF(店舗群別PL!C8=0,0,前提条件!$B$45*店舗群別PL!$B$6*IF(店舗群別PL!C8=1,店舗群別PL!$B$7/12,1))+IF(店舗群別PL!C30=0,0,前提条件!$B$45*店舗群別PL!$B$28*IF(店舗群別PL!C30=1,店舗群別PL!$B$29/12,1))+IF(店舗群別PL!C52=0,0,前提条件!$B$45*店舗群別PL!$B$50*IF(店舗群別PL!C52=1,店舗群別PL!$B$51/12,1))+IF(店舗群別PL!C74=0,0,前提条件!$B$45*店舗群別PL!$B$72*IF(店舗群別PL!C74=1,店舗群別PL!$B$73/12,1))+IF(店舗群別PL!C96=0,0,前提条件!$B$45*店舗群別PL!$B$94*IF(店舗群別PL!C96=1,店舗群別PL!$B$95/12,1)))</f>
@@ -9031,7 +9231,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C10" s="40" t="n">
         <f aca="false">C8+C9</f>
@@ -9039,23 +9239,23 @@
       </c>
       <c r="D10" s="40" t="n">
         <f aca="false">D8+D9</f>
-        <v>-351.8</v>
+        <v>-271.8</v>
       </c>
       <c r="E10" s="40" t="n">
         <f aca="false">E8+E9</f>
-        <v>-373</v>
+        <v>-293</v>
       </c>
       <c r="F10" s="40" t="n">
         <f aca="false">F8+F9</f>
-        <v>-404.2</v>
+        <v>-324.2</v>
       </c>
       <c r="G10" s="40" t="n">
         <f aca="false">G8+G9</f>
-        <v>-435.4</v>
+        <v>-355.4</v>
       </c>
       <c r="H10" s="40" t="n">
         <f aca="false">SUM(C10:G10)</f>
-        <v>-1738.35</v>
+        <v>-1418.35</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9089,7 +9289,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C12" s="38" t="n">
         <f aca="false">-MAX(0,連結PL!C24)*$B$17</f>
@@ -9118,7 +9318,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C13" s="46" t="n">
         <f aca="false">C11+C12+C10</f>
@@ -9126,28 +9326,28 @@
       </c>
       <c r="D13" s="46" t="n">
         <f aca="false">D11+D12+D10</f>
-        <v>-276.54149283</v>
+        <v>-196.54149283</v>
       </c>
       <c r="E13" s="46" t="n">
         <f aca="false">E11+E12+E10</f>
-        <v>-208.90452891</v>
+        <v>-128.90452891</v>
       </c>
       <c r="F13" s="46" t="n">
         <f aca="false">F11+F12+F10</f>
-        <v>-143.51537291</v>
+        <v>-63.5153729100001</v>
       </c>
       <c r="G13" s="46" t="n">
         <f aca="false">G11+G12+G10</f>
-        <v>-77.4262169100001</v>
+        <v>2.57378308999989</v>
       </c>
       <c r="H13" s="40" t="n">
         <f aca="false">SUM(C13:G13)</f>
-        <v>-851.89471456</v>
+        <v>-531.89471456</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C14" s="46" t="n">
         <f aca="false">C13</f>
@@ -9155,24 +9355,24 @@
       </c>
       <c r="D14" s="46" t="n">
         <f aca="false">C14+D13</f>
-        <v>-422.04859583</v>
+        <v>-342.04859583</v>
       </c>
       <c r="E14" s="46" t="n">
         <f aca="false">D14+E13</f>
-        <v>-630.95312474</v>
+        <v>-470.95312474</v>
       </c>
       <c r="F14" s="46" t="n">
         <f aca="false">E14+F13</f>
-        <v>-774.46849765</v>
+        <v>-534.46849765</v>
       </c>
       <c r="G14" s="46" t="n">
         <f aca="false">F14+G13</f>
-        <v>-851.89471456</v>
+        <v>-531.89471456</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -9184,52 +9384,52 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B17" s="23" t="n">
         <v>0.3</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B18" s="49" t="n">
         <f aca="false">-MIN(C14:G14)</f>
-        <v>851.89471456</v>
+        <v>534.46849765</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B19" s="22" t="n">
         <v>200</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B20" s="22" t="n">
         <v>150</v>
       </c>
       <c r="J20" s="24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B21" s="29" t="n">
         <f aca="false">B19+B20</f>
@@ -9243,20 +9443,20 @@
       </c>
       <c r="B22" s="28" t="n">
         <f aca="false">B21-B18</f>
-        <v>-501.89471456</v>
+        <v>-184.46849765</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="50" t="s">
-        <v>157</v>
+      <c r="A25" s="30" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
